--- a/jogos_2024-09-02.xlsx
+++ b/jogos_2024-09-02.xlsx
@@ -633,7 +633,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -643,25 +643,25 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>SCM Gloria Buzău</t>
         </is>
       </c>
       <c r="G2" t="n">
         <v>2</v>
       </c>
       <c r="H2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -672,19 +672,19 @@
         <v>2.1</v>
       </c>
       <c r="M2" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="N2" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="O2" t="n">
-        <v>2.63</v>
+        <v>2.88</v>
       </c>
       <c r="P2" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="R2" t="n">
         <v>1.44</v>
@@ -699,53 +699,53 @@
         <v>1.33</v>
       </c>
       <c r="V2" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="W2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X2" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>['45+7', '90+3']</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>['65']</t>
+        </is>
+      </c>
+      <c r="AG2" t="n">
         <v>1.28</v>
       </c>
-      <c r="X2" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>['39', '42']</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>['26', '82']</t>
-        </is>
-      </c>
-      <c r="AG2" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH2" t="n">
-        <v>1.6</v>
+        <v>1.71</v>
       </c>
       <c r="AI2" t="n">
         <v>1.67</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="AK2" s="3" t="n">
         <v>45537.54166666666</v>
@@ -772,109 +772,109 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Hapoel Umm al-Fahm</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ironi Ramat HaSharon</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="M3" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="X3" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD3" t="n">
         <v>2</v>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="M3" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N3" t="n">
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>['46', '90+1']</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>['49']</t>
+        </is>
+      </c>
+      <c r="AG3" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AI3" t="n">
         <v>2.1</v>
       </c>
-      <c r="O3" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="P3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X3" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>['37', '45', '64']</t>
-        </is>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>2.3</v>
-      </c>
       <c r="AJ3" t="n">
-        <v>1.62</v>
+        <v>1.83</v>
       </c>
       <c r="AK3" s="3" t="n">
         <v>45537.54166666666</v>
@@ -901,109 +901,109 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G4" t="n">
         <v>2</v>
       </c>
       <c r="H4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J4" t="n">
         <v>1</v>
       </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="M4" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O4" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T4" t="n">
         <v>3.25</v>
       </c>
-      <c r="N4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O4" t="n">
+      <c r="U4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA4" t="n">
         <v>3.2</v>
       </c>
-      <c r="P4" t="n">
+      <c r="AB4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD4" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q4" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S4" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="X4" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>2</v>
-      </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>['46', '90+1']</t>
+          <t>['39', '42']</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>['49']</t>
+          <t>['26', '82']</t>
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.47</v>
+        <v>1.33</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.38</v>
+        <v>1.6</v>
       </c>
       <c r="AI4" t="n">
-        <v>2.1</v>
+        <v>1.67</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.83</v>
+        <v>2.38</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45537.54166666666</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,109 +1030,109 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Hapoel Umm al-Fahm</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>SCM Gloria Buzău</t>
+          <t>Ironi Ramat HaSharon</t>
         </is>
       </c>
       <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>3</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
         <v>2</v>
       </c>
-      <c r="H5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L5" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="M5" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N5" t="n">
         <v>2.1</v>
       </c>
-      <c r="M5" t="n">
-        <v>3</v>
-      </c>
-      <c r="N5" t="n">
-        <v>3.55</v>
-      </c>
       <c r="O5" t="n">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="P5" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="Q5" t="n">
-        <v>4</v>
+        <v>2.63</v>
       </c>
       <c r="R5" t="n">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="S5" t="n">
-        <v>2.63</v>
+        <v>3.5</v>
       </c>
       <c r="T5" t="n">
-        <v>3.25</v>
+        <v>2.25</v>
       </c>
       <c r="U5" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="V5" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="W5" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="X5" t="n">
-        <v>3.2</v>
+        <v>4.2</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.21</v>
+        <v>1.6</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.65</v>
+        <v>2.3</v>
       </c>
       <c r="AA5" t="n">
-        <v>4</v>
+        <v>2.55</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.2</v>
+        <v>1.48</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.83</v>
+        <v>1.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.83</v>
+        <v>2.5</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>['45+7', '90+3']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>['65']</t>
+          <t>['37', '45', '64']</t>
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.28</v>
+        <v>1.42</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.71</v>
+        <v>1.53</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.67</v>
+        <v>2.3</v>
       </c>
       <c r="AJ5" t="n">
-        <v>2.5</v>
+        <v>1.62</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45537.54166666666</v>
@@ -1278,29 +1278,29 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G7" t="n">
         <v>2</v>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
@@ -1314,83 +1314,83 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.05</v>
+        <v>3.35</v>
       </c>
       <c r="M7" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="N7" t="n">
-        <v>3.5</v>
+        <v>1.95</v>
       </c>
       <c r="O7" t="n">
-        <v>2.63</v>
+        <v>3.4</v>
       </c>
       <c r="P7" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.33</v>
+        <v>2.3</v>
       </c>
       <c r="R7" t="n">
-        <v>1.4</v>
+        <v>1.24</v>
       </c>
       <c r="S7" t="n">
-        <v>2.75</v>
+        <v>3.8</v>
       </c>
       <c r="T7" t="n">
-        <v>3</v>
+        <v>2.13</v>
       </c>
       <c r="U7" t="n">
-        <v>1.36</v>
+        <v>1.67</v>
       </c>
       <c r="V7" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X7" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>['55', '63']</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>['31']</t>
+        </is>
+      </c>
+      <c r="AG7" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AH7" t="n">
         <v>1.29</v>
       </c>
-      <c r="X7" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>['47', '90+2']</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>['4', '79']</t>
-        </is>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1.79</v>
-      </c>
       <c r="AI7" t="n">
-        <v>1.62</v>
+        <v>2.2</v>
       </c>
       <c r="AJ7" t="n">
-        <v>2.5</v>
+        <v>1.66</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45537.58333333334</v>
@@ -1417,25 +1417,25 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Levanger</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G8" t="n">
         <v>2</v>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -1443,83 +1443,83 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.25</v>
+        <v>1.67</v>
       </c>
       <c r="M8" t="n">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="N8" t="n">
-        <v>2.65</v>
+        <v>4.2</v>
       </c>
       <c r="O8" t="n">
-        <v>2.63</v>
+        <v>2.05</v>
       </c>
       <c r="P8" t="n">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.41</v>
+        <v>4</v>
       </c>
       <c r="R8" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="S8" t="n">
         <v>3.7</v>
       </c>
       <c r="T8" t="n">
-        <v>2.19</v>
+        <v>1.95</v>
       </c>
       <c r="U8" t="n">
-        <v>1.61</v>
+        <v>1.72</v>
       </c>
       <c r="V8" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W8" t="n">
-        <v>1.16</v>
+        <v>1.09</v>
       </c>
       <c r="X8" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.62</v>
+        <v>2.69</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.21</v>
+        <v>2.05</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.75</v>
+        <v>2.58</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>['12', '87']</t>
+          <t>['57', '90+3']</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>['31']</t>
+          <t>['13', '42', '61']</t>
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.41</v>
+        <v>1.22</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.62</v>
+        <v>2.15</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.77</v>
+        <v>1.57</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2.05</v>
+        <v>2.5</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45537.58333333334</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,19 +1546,19 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
         <v>2</v>
-      </c>
-      <c r="H9" t="n">
-        <v>3</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -1572,83 +1572,83 @@
         </is>
       </c>
       <c r="L9" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="M9" t="n">
+        <v>6</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O9" t="n">
+        <v>8</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="Q9" t="n">
         <v>1.67</v>
       </c>
-      <c r="M9" t="n">
+      <c r="R9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S9" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X9" t="n">
         <v>3.9</v>
       </c>
-      <c r="N9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="O9" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="P9" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>4</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S9" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X9" t="n">
-        <v>5.8</v>
-      </c>
       <c r="Y9" t="n">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.69</v>
+        <v>2.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.05</v>
+        <v>2.72</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.75</v>
+        <v>1.38</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.44</v>
+        <v>2</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.58</v>
+        <v>1.73</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>['57', '90+3']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>['13', '42', '61']</t>
+          <t>['19', '22']</t>
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.22</v>
+        <v>3.94</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.15</v>
+        <v>1.01</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.57</v>
+        <v>4.5</v>
       </c>
       <c r="AJ9" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45537.58333333334</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,25 +1675,25 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1701,83 +1701,83 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.35</v>
+        <v>2.4</v>
       </c>
       <c r="M10" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="N10" t="n">
-        <v>1.95</v>
+        <v>2.63</v>
       </c>
       <c r="O10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q10" t="n">
         <v>3.4</v>
       </c>
-      <c r="P10" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2.3</v>
-      </c>
       <c r="R10" t="n">
-        <v>1.24</v>
+        <v>1.44</v>
       </c>
       <c r="S10" t="n">
-        <v>3.8</v>
+        <v>2.63</v>
       </c>
       <c r="T10" t="n">
-        <v>2.13</v>
+        <v>3</v>
       </c>
       <c r="U10" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X10" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Z10" t="n">
         <v>1.67</v>
       </c>
-      <c r="V10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X10" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2.27</v>
-      </c>
       <c r="AA10" t="n">
-        <v>2.15</v>
+        <v>3.6</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.66</v>
+        <v>1.25</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.44</v>
+        <v>1.83</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.62</v>
+        <v>1.83</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>['55', '63']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>['31']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AI10" t="n">
         <v>1.83</v>
       </c>
-      <c r="AH10" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AI10" t="n">
+      <c r="AJ10" t="n">
         <v>2.2</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.66</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45537.58333333334</v>
@@ -1794,119 +1794,119 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H11" t="n">
+        <v>2</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
         <v>1</v>
       </c>
-      <c r="I11" t="n">
-        <v>2</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
       <c r="K11" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.8</v>
+        <v>2.05</v>
       </c>
       <c r="M11" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="N11" t="n">
-        <v>2.3</v>
+        <v>3.5</v>
       </c>
       <c r="O11" t="n">
-        <v>3.92</v>
+        <v>2.63</v>
       </c>
       <c r="P11" t="n">
-        <v>2.28</v>
+        <v>2.1</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.68</v>
+        <v>4.33</v>
       </c>
       <c r="R11" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="S11" t="n">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="T11" t="n">
-        <v>2.65</v>
+        <v>3</v>
       </c>
       <c r="U11" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="V11" t="n">
         <v>1.02</v>
       </c>
       <c r="W11" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="X11" t="n">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.82</v>
+        <v>2.05</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.96</v>
+        <v>1.67</v>
       </c>
       <c r="AA11" t="n">
-        <v>3</v>
+        <v>3.34</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>['10', '16', '76', '88']</t>
+          <t>['47', '90+2']</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>['67']</t>
+          <t>['4', '79']</t>
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.6</v>
+        <v>1.29</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.27</v>
+        <v>1.79</v>
       </c>
       <c r="AI11" t="n">
-        <v>2.3</v>
+        <v>1.62</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45537.58333333334</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,25 +1933,25 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Levanger</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1959,83 +1959,83 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="M12" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="N12" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="O12" t="n">
         <v>2.63</v>
       </c>
-      <c r="O12" t="n">
-        <v>3.1</v>
-      </c>
       <c r="P12" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="X12" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>['12', '87']</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>['31']</t>
+        </is>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AJ12" t="n">
         <v>2.05</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T12" t="n">
-        <v>3</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="X12" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>2.2</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45537.58333333334</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,25 +2062,25 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H13" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" t="n">
         <v>2</v>
       </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
       <c r="J13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -2088,83 +2088,83 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>7.5</v>
+        <v>2.8</v>
       </c>
       <c r="M13" t="n">
-        <v>6</v>
+        <v>3.25</v>
       </c>
       <c r="N13" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="O13" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W13" t="n">
         <v>1.25</v>
       </c>
-      <c r="O13" t="n">
-        <v>8</v>
-      </c>
-      <c r="P13" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.2</v>
-      </c>
       <c r="X13" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.5</v>
+        <v>1.82</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.5</v>
+        <v>1.96</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.72</v>
+        <v>3</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AC13" t="n">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.73</v>
+        <v>2.05</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['10', '16', '76', '88']</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>['19', '22']</t>
+          <t>['67']</t>
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>3.94</v>
+        <v>1.6</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="AI13" t="n">
-        <v>4.5</v>
+        <v>2.3</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45537.58333333334</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,23 +2191,23 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Sloven Ruma</t>
         </is>
       </c>
       <c r="G14" t="n">
+        <v>5</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
         <v>3</v>
       </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>1</v>
-      </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
@@ -2217,65 +2217,65 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.57</v>
+        <v>1.53</v>
       </c>
       <c r="M14" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="N14" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>7</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X14" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC14" t="n">
         <v>1.85</v>
       </c>
-      <c r="N14" t="n">
-        <v>5.58</v>
-      </c>
-      <c r="O14" t="n">
-        <v>3</v>
-      </c>
-      <c r="P14" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="X14" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AD14" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>['32', '63', '86']</t>
+          <t>['7', '27', '40', '50', '67']</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -2284,16 +2284,16 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>1.45</v>
+        <v>1.08</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.48</v>
+        <v>2.15</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.95</v>
+        <v>1.22</v>
       </c>
       <c r="AJ14" t="n">
-        <v>2.1</v>
+        <v>4.75</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45537.625</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,109 +2320,109 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sloven Ruma</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
       <c r="I15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="N15" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="O15" t="n">
         <v>3</v>
       </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L15" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="M15" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="N15" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="O15" t="n">
-        <v>1.8</v>
-      </c>
       <c r="P15" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>7</v>
+        <v>3.4</v>
       </c>
       <c r="R15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W15" t="n">
         <v>1.29</v>
       </c>
-      <c r="S15" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="U15" t="n">
+      <c r="X15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>['32', '63', '86']</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG15" t="n">
         <v>1.45</v>
       </c>
-      <c r="V15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X15" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Z15" t="n">
+      <c r="AH15" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AI15" t="n">
         <v>1.95</v>
       </c>
-      <c r="AA15" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>['7', '27', '40', '50', '67']</t>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AJ15" t="n">
-        <v>4.75</v>
+        <v>2.1</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45537.625</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,109 +2578,109 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Foggia</t>
         </is>
       </c>
       <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
         <v>1</v>
       </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>1</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
       <c r="K17" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L17" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="M17" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="O17" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R17" t="n">
         <v>1.53</v>
       </c>
-      <c r="M17" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N17" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="O17" t="n">
+      <c r="S17" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AC17" t="n">
         <v>2.1</v>
       </c>
-      <c r="P17" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X17" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z17" t="n">
+      <c r="AD17" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>['10', '60']</t>
+        </is>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AJ17" t="n">
         <v>1.8</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>['2']</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>3.6</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45537.65625</v>
@@ -2707,22 +2707,22 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Foggia</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18" t="n">
         <v>1</v>
@@ -2736,80 +2736,80 @@
         <v>2.9</v>
       </c>
       <c r="M18" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="N18" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="O18" t="n">
         <v>3.75</v>
       </c>
       <c r="P18" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X18" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC18" t="n">
         <v>1.91</v>
       </c>
-      <c r="Q18" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T18" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="X18" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AD18" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['39', '52']</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>['10', '60']</t>
+          <t>['45']</t>
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AI18" t="n">
         <v>2.38</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45537.65625</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,22 +2836,22 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2862,83 +2862,83 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3</v>
+        <v>1.95</v>
       </c>
       <c r="M19" t="n">
         <v>2.9</v>
       </c>
       <c r="N19" t="n">
-        <v>2.3</v>
+        <v>3.9</v>
       </c>
       <c r="O19" t="n">
-        <v>3.75</v>
+        <v>2.75</v>
       </c>
       <c r="P19" t="n">
         <v>1.91</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.1</v>
+        <v>4.5</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="S19" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="T19" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="U19" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="V19" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="W19" t="n">
-        <v>1.38</v>
+        <v>1.52</v>
       </c>
       <c r="X19" t="n">
-        <v>2.71</v>
+        <v>2.4</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AA19" t="n">
-        <v>4.05</v>
+        <v>5.5</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AD19" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>['83']</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>['51']</t>
+        </is>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AI19" t="n">
         <v>1.67</v>
       </c>
-      <c r="AE19" t="inlineStr">
-        <is>
-          <t>['29', '34', '87']</t>
-        </is>
-      </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>2.4</v>
-      </c>
       <c r="AJ19" t="n">
-        <v>1.83</v>
+        <v>2.88</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45537.65625</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,25 +2965,25 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G20" t="n">
+        <v>3</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
         <v>2</v>
       </c>
-      <c r="H20" t="n">
-        <v>1</v>
-      </c>
-      <c r="I20" t="n">
-        <v>1</v>
-      </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -2991,83 +2991,83 @@
         </is>
       </c>
       <c r="L20" t="n">
+        <v>3</v>
+      </c>
+      <c r="M20" t="n">
         <v>2.9</v>
       </c>
-      <c r="M20" t="n">
-        <v>3.25</v>
-      </c>
       <c r="N20" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="O20" t="n">
         <v>3.75</v>
       </c>
       <c r="P20" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="R20" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="S20" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="T20" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="U20" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="V20" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="W20" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="X20" t="n">
-        <v>3.3</v>
+        <v>2.71</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="Z20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD20" t="n">
         <v>1.67</v>
       </c>
-      <c r="AA20" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>['39', '52']</t>
+          <t>['29', '34', '87']</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>['45']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.58</v>
+        <v>1.49</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AI20" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45537.65625</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,23 +3094,23 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="G21" t="n">
         <v>1</v>
       </c>
       <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
         <v>1</v>
       </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
@@ -3120,83 +3120,83 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.95</v>
+        <v>1.53</v>
       </c>
       <c r="M21" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="N21" t="n">
-        <v>3.9</v>
+        <v>6.25</v>
       </c>
       <c r="O21" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S21" t="n">
         <v>2.75</v>
       </c>
-      <c r="P21" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2.25</v>
-      </c>
       <c r="T21" t="n">
-        <v>3.75</v>
+        <v>3</v>
       </c>
       <c r="U21" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="V21" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="W21" t="n">
-        <v>1.52</v>
+        <v>1.28</v>
       </c>
       <c r="X21" t="n">
-        <v>2.4</v>
+        <v>3.18</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.63</v>
+        <v>2</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.44</v>
+        <v>1.8</v>
       </c>
       <c r="AA21" t="n">
-        <v>5.5</v>
+        <v>3.28</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.11</v>
+        <v>1.27</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>['83']</t>
+          <t>['2']</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>['51']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.57</v>
+        <v>2.04</v>
       </c>
       <c r="AI21" t="n">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="AJ21" t="n">
-        <v>2.88</v>
+        <v>3.6</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45537.65625</v>
@@ -3342,29 +3342,29 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>HFX Wanderers FC</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
         <v>1</v>
@@ -3378,83 +3378,83 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.12</v>
+        <v>2.5</v>
       </c>
       <c r="M23" t="n">
-        <v>3.38</v>
+        <v>3.3</v>
       </c>
       <c r="N23" t="n">
-        <v>3.04</v>
+        <v>2.5</v>
       </c>
       <c r="O23" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="P23" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="Q23" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="R23" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="S23" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="T23" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="U23" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="V23" t="n">
         <v>1.03</v>
       </c>
       <c r="W23" t="n">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="X23" t="n">
-        <v>3.3</v>
+        <v>3.92</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.81</v>
+        <v>1.66</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.92</v>
+        <v>2.05</v>
       </c>
       <c r="AA23" t="n">
-        <v>3.2</v>
+        <v>2.64</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>['22', '67']</t>
+          <t>['42']</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>['76']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.38</v>
+        <v>1.63</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.62</v>
+        <v>1.37</v>
       </c>
       <c r="AI23" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45537.66666666666</v>
@@ -3471,29 +3471,29 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>HFX Wanderers FC</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="G24" t="n">
+        <v>2</v>
+      </c>
+      <c r="H24" t="n">
         <v>1</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
       </c>
       <c r="I24" t="n">
         <v>1</v>
@@ -3507,83 +3507,83 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.5</v>
+        <v>2.12</v>
       </c>
       <c r="M24" t="n">
-        <v>3.3</v>
+        <v>3.38</v>
       </c>
       <c r="N24" t="n">
-        <v>2.5</v>
+        <v>3.04</v>
       </c>
       <c r="O24" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="P24" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="Q24" t="n">
+        <v>3</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3</v>
+      </c>
+      <c r="T24" t="n">
         <v>2.75</v>
       </c>
-      <c r="R24" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S24" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.63</v>
-      </c>
       <c r="U24" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="V24" t="n">
         <v>1.03</v>
       </c>
       <c r="W24" t="n">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="X24" t="n">
-        <v>3.92</v>
+        <v>3.3</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.66</v>
+        <v>1.81</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.05</v>
+        <v>1.92</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.64</v>
+        <v>3.2</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>['42']</t>
+          <t>['22', '67']</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['76']</t>
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.63</v>
+        <v>1.38</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.37</v>
+        <v>1.62</v>
       </c>
       <c r="AI24" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45537.66666666666</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,19 +4513,19 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Austin II</t>
         </is>
       </c>
       <c r="G32" t="n">
+        <v>3</v>
+      </c>
+      <c r="H32" t="n">
         <v>2</v>
-      </c>
-      <c r="H32" t="n">
-        <v>3</v>
       </c>
       <c r="I32" t="n">
         <v>1</v>
@@ -4539,83 +4539,83 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.4</v>
+        <v>1.67</v>
       </c>
       <c r="M32" t="n">
-        <v>2.9</v>
+        <v>3.75</v>
       </c>
       <c r="N32" t="n">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="O32" t="n">
-        <v>3.4</v>
+        <v>2.25</v>
       </c>
       <c r="P32" t="n">
-        <v>1.91</v>
+        <v>2.38</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.4</v>
+        <v>4.33</v>
       </c>
       <c r="R32" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S32" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X32" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>['14', '73', '89']</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>['4', '28']</t>
+        </is>
+      </c>
+      <c r="AG32" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AI32" t="n">
         <v>1.5</v>
       </c>
-      <c r="S32" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T32" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V32" t="n">
-        <v>0</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X32" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AE32" t="inlineStr">
-        <is>
-          <t>['21', '50']</t>
-        </is>
-      </c>
-      <c r="AF32" t="inlineStr">
-        <is>
-          <t>['4', '16', '72']</t>
-        </is>
-      </c>
-      <c r="AG32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AJ32" t="n">
-        <v>2.1</v>
+        <v>2.75</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45537.83333333334</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,19 +4642,19 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Austin II</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G33" t="n">
+        <v>2</v>
+      </c>
+      <c r="H33" t="n">
         <v>3</v>
-      </c>
-      <c r="H33" t="n">
-        <v>2</v>
       </c>
       <c r="I33" t="n">
         <v>1</v>
@@ -4668,83 +4668,83 @@
         </is>
       </c>
       <c r="L33" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="M33" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N33" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O33" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P33" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S33" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T33" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X33" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD33" t="n">
         <v>1.67</v>
       </c>
-      <c r="M33" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="N33" t="n">
-        <v>4</v>
-      </c>
-      <c r="O33" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="P33" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="R33" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S33" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="T33" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="U33" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="V33" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X33" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AD33" t="n">
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>['21', '50']</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>['4', '16', '72']</t>
+        </is>
+      </c>
+      <c r="AG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="n">
         <v>2.1</v>
       </c>
-      <c r="AE33" t="inlineStr">
-        <is>
-          <t>['14', '73', '89']</t>
-        </is>
-      </c>
-      <c r="AF33" t="inlineStr">
-        <is>
-          <t>['4', '28']</t>
-        </is>
-      </c>
-      <c r="AG33" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AJ33" t="n">
-        <v>2.75</v>
+        <v>2.1</v>
       </c>
       <c r="AK33" s="3" t="n">
         <v>45537.83333333334</v>
